--- a/outputs/q4/q4_resource_requirements.xlsx
+++ b/outputs/q4/q4_resource_requirements.xlsx
@@ -632,7 +632,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>strict_no_duplication-K2-P003</t>
+          <t>strict_no_duplication-K2-P001</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -642,86 +642,90 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S001,S002,S003,S004,S005,S007,S008,S009,S010,S011,S012,S013,S014,S015</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Q2-012,Q2-024</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>Q2-003,Q2-004,Q2-005,Q2-006,Q2-007,Q2-008,Q2-009,Q2-010,Q2-011,Q2-012,Q2-013,Q2-014,Q2-015,Q2-016,Q2-018,Q2-019,Q2-020,Q2-021,Q2-022,Q2-023,Q2-024,Q2-025,Q2-026</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Q3-R01,Q3-R02,Q3-R03,Q3-R04</t>
+        </is>
+      </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I2" t="n">
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="J2" t="n">
-        <v>154</v>
+        <v>699</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>3186.338154658319</v>
+        <v>47548.40551964469</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>12227.9291242279</v>
       </c>
       <c r="W2" t="n">
-        <v>3186.338154658319</v>
+        <v>59776.33464387259</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z2" t="n">
         <v>2</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -735,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>strict_no_duplication-K2-P003</t>
+          <t>strict_no_duplication-K2-P001</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -745,90 +749,86 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S006,S007,S008,S009,S010,S011,S012,S013,S014,S015</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Q2-001,Q2-002,Q2-003,Q2-004,Q2-005,Q2-006,Q2-007,Q2-008,Q2-009,Q2-010,Q2-011,Q2-013,Q2-014,Q2-015,Q2-016,Q2-017,Q2-018,Q2-019,Q2-020,Q2-021,Q2-022,Q2-023,Q2-025,Q2-026</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Q3-R01,Q3-R02,Q3-R03,Q3-R04,Q3-R05</t>
-        </is>
-      </c>
+          <t>Q2-001,Q2-002,Q2-017</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="J3" t="n">
-        <v>604</v>
+        <v>59</v>
       </c>
       <c r="K3" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="L3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>49114.24641431004</v>
+        <v>3728.020703809979</v>
       </c>
       <c r="V3" t="n">
-        <v>13336.08268253881</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>62450.32909684885</v>
+        <v>3728.020703809979</v>
       </c>
       <c r="X3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
         <v>2</v>
       </c>
       <c r="Z3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AB3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AC3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -857,7 +857,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Q2-012,Q2-024</t>
+          <t>Q2-005,Q2-022</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -883,7 +883,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Q2-001,Q2-002,Q2-003,Q2-004,Q2-005,Q2-006,Q2-007,Q2-009,Q2-010,Q2-011,Q2-013,Q2-014,Q2-015,Q2-016,Q2-017,Q2-018,Q2-019,Q2-021,Q2-023,Q2-025,Q2-026</t>
+          <t>Q2-003,Q2-004,Q2-006,Q2-007,Q2-008,Q2-009,Q2-010,Q2-011,Q2-012,Q2-013,Q2-014,Q2-015,Q2-016,Q2-018,Q2-019,Q2-020,Q2-021,Q2-023,Q2-024,Q2-025,Q2-026</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Q3-R01,Q3-R02,Q3-R03,Q3-R04,Q3-R05</t>
+          <t>Q3-R01,Q3-R02,Q3-R03,Q3-R04</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -981,7 +981,7 @@
         <v>21</v>
       </c>
       <c r="L5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M5" t="n">
         <v>4</v>
@@ -996,10 +996,10 @@
         <v>6</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
@@ -1008,13 +1008,13 @@
         <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>45386.22571050007</v>
+        <v>44362.06736498636</v>
       </c>
       <c r="V5" t="n">
-        <v>13336.08268253881</v>
+        <v>12227.9291242279</v>
       </c>
       <c r="W5" t="n">
-        <v>58722.30839303887</v>
+        <v>56589.99648921426</v>
       </c>
       <c r="X5" t="n">
         <v>4</v>
@@ -1029,16 +1029,16 @@
         <v>6</v>
       </c>
       <c r="AB5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD5" t="n">
         <v>2</v>
       </c>
       <c r="AE5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Q2-008,Q2-020,Q2-022</t>
+          <t>Q2-001,Q2-002,Q2-017</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1132,7 +1132,7 @@
         <v>1</v>
       </c>
       <c r="AB6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>replicate_relay-K2-P031</t>
+          <t>replicate_relay-K2-P008</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1165,86 +1165,90 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S001,S002,S003,S004,S005,S007,S008,S009,S010,S011,S012,S013,S014,S015</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Q2-012,Q2-024</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>Q2-003,Q2-004,Q2-005,Q2-006,Q2-007,Q2-008,Q2-009,Q2-010,Q2-011,Q2-012,Q2-013,Q2-014,Q2-015,Q2-016,Q2-018,Q2-019,Q2-020,Q2-021,Q2-022,Q2-023,Q2-024,Q2-025,Q2-026</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>K2-G1-Q3-R01,K2-G1-Q3-R02,K2-G1-Q3-R03,K2-G1-Q3-R04</t>
+        </is>
+      </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I7" t="n">
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="J7" t="n">
-        <v>154</v>
+        <v>699</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U7" t="n">
-        <v>3186.338154658319</v>
+        <v>47548.40551964469</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>12227.9291242279</v>
       </c>
       <c r="W7" t="n">
-        <v>3186.338154658319</v>
+        <v>59776.33464387259</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z7" t="n">
         <v>2</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -1258,7 +1262,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>replicate_relay-K2-P031</t>
+          <t>replicate_relay-K2-P008</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1268,90 +1272,86 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S006,S007,S008,S009,S010,S011,S012,S013,S014,S015</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Q2-001,Q2-002,Q2-003,Q2-004,Q2-005,Q2-006,Q2-007,Q2-008,Q2-009,Q2-010,Q2-011,Q2-013,Q2-014,Q2-015,Q2-016,Q2-017,Q2-018,Q2-019,Q2-020,Q2-021,Q2-022,Q2-023,Q2-025,Q2-026</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>K2-G2-Q3-R01,K2-G2-Q3-R02,K2-G2-Q3-R03,K2-G2-Q3-R04,K2-G2-Q3-R05</t>
-        </is>
-      </c>
+          <t>Q2-001,Q2-002,Q2-017</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
-        <v>604</v>
+        <v>59</v>
       </c>
       <c r="K8" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>49114.24641431004</v>
+        <v>3728.020703809979</v>
       </c>
       <c r="V8" t="n">
-        <v>13336.08268253881</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>62450.32909684885</v>
+        <v>3728.020703809979</v>
       </c>
       <c r="X8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
         <v>2</v>
       </c>
       <c r="Z8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AB8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>replicate_relay-K3-P059</t>
+          <t>replicate_relay-K3-P077</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Q2-012,Q2-024</t>
+          <t>Q2-005,Q2-022</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1406,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>replicate_relay-K3-P059</t>
+          <t>replicate_relay-K3-P077</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Q2-001,Q2-002,Q2-003,Q2-004,Q2-005,Q2-006,Q2-007,Q2-009,Q2-010,Q2-011,Q2-013,Q2-014,Q2-015,Q2-016,Q2-017,Q2-018,Q2-019,Q2-021,Q2-023,Q2-025,Q2-026</t>
+          <t>Q2-003,Q2-004,Q2-006,Q2-007,Q2-008,Q2-009,Q2-010,Q2-011,Q2-012,Q2-013,Q2-014,Q2-015,Q2-016,Q2-018,Q2-019,Q2-020,Q2-021,Q2-023,Q2-024,Q2-025,Q2-026</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>K3-G2-Q3-R01,K3-G2-Q3-R02,K3-G2-Q3-R03,K3-G2-Q3-R04,K3-G2-Q3-R05</t>
+          <t>K3-G2-Q3-R01,K3-G2-Q3-R02,K3-G2-Q3-R03,K3-G2-Q3-R04</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1504,7 +1504,7 @@
         <v>21</v>
       </c>
       <c r="L10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M10" t="n">
         <v>4</v>
@@ -1519,10 +1519,10 @@
         <v>6</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S10" t="n">
         <v>2</v>
@@ -1531,13 +1531,13 @@
         <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>45386.22571050007</v>
+        <v>44362.06736498636</v>
       </c>
       <c r="V10" t="n">
-        <v>13336.08268253881</v>
+        <v>12227.9291242279</v>
       </c>
       <c r="W10" t="n">
-        <v>58722.30839303887</v>
+        <v>56589.99648921426</v>
       </c>
       <c r="X10" t="n">
         <v>4</v>
@@ -1552,16 +1552,16 @@
         <v>6</v>
       </c>
       <c r="AB10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD10" t="n">
         <v>2</v>
       </c>
       <c r="AE10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>replicate_relay-K3-P059</t>
+          <t>replicate_relay-K3-P077</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Q2-008,Q2-020,Q2-022</t>
+          <t>Q2-001,Q2-002,Q2-017</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1655,7 +1655,7 @@
         <v>1</v>
       </c>
       <c r="AB11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
